--- a/output/pdf_financials_xlsx/PWI.xlsx
+++ b/output/pdf_financials_xlsx/PWI.xlsx
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003137</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.370054</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.243141</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.339362</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.314067</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.211122</v>
       </c>
     </row>
     <row r="35">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.370054</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.243141</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.339362</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.314067</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.211122</v>
       </c>
     </row>
     <row r="37">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">

--- a/output/pdf_financials_xlsx/PWI.xlsx
+++ b/output/pdf_financials_xlsx/PWI.xlsx
@@ -524,10 +524,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -580,10 +578,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.313658</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.484316</v>
@@ -604,10 +600,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -628,10 +622,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -652,10 +644,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.313658</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.484316</v>
@@ -708,10 +698,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -732,10 +720,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -756,10 +742,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -780,10 +764,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -836,10 +818,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0.039464</v>
@@ -956,10 +936,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -980,10 +958,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1164,10 +1140,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -2880,10 +2854,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2904,10 +2876,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -2928,10 +2898,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2952,10 +2920,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -2976,10 +2942,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.055725</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.028374</v>
@@ -3000,10 +2964,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -3024,10 +2986,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.055725</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.028374</v>
@@ -3048,10 +3008,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0</v>
@@ -3072,10 +3030,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -3096,10 +3052,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -3120,10 +3074,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -3144,10 +3096,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -3168,10 +3118,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -3192,10 +3140,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -3216,10 +3162,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -3240,10 +3184,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -3264,10 +3206,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -3288,10 +3228,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -3312,10 +3250,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -3336,10 +3272,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -3360,10 +3294,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -3384,10 +3316,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -3408,10 +3338,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -3432,10 +3360,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -3456,10 +3382,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -3480,10 +3404,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -3504,10 +3426,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -3560,10 +3480,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -3584,10 +3502,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>61.752106</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>6.750336</v>
@@ -3608,10 +3524,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>-0.000915</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.370054</v>
@@ -3632,10 +3546,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -3656,10 +3568,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.370969</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-0.130937</v>
@@ -3680,10 +3590,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.370054</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.243141</v>
@@ -3704,10 +3612,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3728,10 +3634,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-61.381137</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-6.881273</v>
@@ -3757,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I247"/>
+  <dimension ref="A1:I272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5229,10 +5133,8 @@
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="5" t="n">
+        <v>3.183247</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>-10.698818</v>
@@ -5264,10 +5166,8 @@
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>0.000915</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>-0.004024</v>
@@ -5334,10 +5234,8 @@
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="5" t="n">
+        <v>-7.241422</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>4.361588</v>
@@ -5404,10 +5302,8 @@
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="5" t="n">
+        <v>0.0008319999999999999</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>-0.046183</v>
@@ -5439,10 +5335,8 @@
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="5" t="n">
+        <v>0.280317</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>-0.380379</v>
@@ -5474,10 +5368,8 @@
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="5" t="n">
+        <v>0.402708</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>0.06381299999999999</v>
@@ -5546,10 +5438,8 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="5" t="n">
+        <v>-0.126994</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>-0.047287</v>
@@ -5622,10 +5512,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="5" t="n">
+        <v>0.055725</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0.028374</v>
@@ -5731,10 +5619,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="5" t="n">
+        <v>-61.381137</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>-6.881273</v>
@@ -5887,10 +5773,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="5" t="n">
+        <v>61.752106</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>6.750336</v>
@@ -5926,10 +5810,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>0.370969</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>-0.130937</v>
@@ -5961,10 +5843,8 @@
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="5" t="n">
+        <v>-0.000915</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>0.004024</v>
@@ -6460,10 +6340,8 @@
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="5" t="n">
+        <v>30.824077</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>4.391537</v>
@@ -6495,10 +6373,8 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="5" t="n">
+        <v>32.503805</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>-9.054918000000001</v>
@@ -6676,10 +6552,8 @@
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="5" t="n">
+        <v>3.3e-06</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>5.2e-06</v>
@@ -7060,10 +6934,8 @@
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="5" t="n">
+        <v>1.5e-06</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>3.2e-06</v>
@@ -7263,10 +7135,8 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="5" t="n">
+        <v>-1.288731</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>-2.713601</v>
@@ -7300,10 +7170,8 @@
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>0.584153</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>1.642045</v>
@@ -7454,10 +7322,8 @@
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E98" s="5" t="n">
+        <v>3.7e-06</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>3.8e-06</v>
@@ -7807,10 +7673,8 @@
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="5" t="n">
+        <v>32.21666</v>
       </c>
       <c r="F107" s="5" t="n">
         <v>4.568975</v>
@@ -7889,10 +7753,8 @@
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="5" t="n">
+        <v>-1.392583</v>
       </c>
       <c r="F109" s="5" t="n">
         <v>-0.177438</v>
@@ -7930,10 +7792,8 @@
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="5" t="n">
+        <v>1.288438</v>
       </c>
       <c r="F110" s="5" t="n">
         <v>1.570036</v>
@@ -8014,10 +7874,8 @@
           <t>InterestPaidSupplementalData</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="5" t="n">
+        <v>0.000413</v>
       </c>
       <c r="F112" s="5" t="n">
         <v>0.000133</v>
@@ -8092,10 +7950,8 @@
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="5" t="n">
+        <v>3.183247</v>
       </c>
       <c r="F114" s="5" t="n">
         <v>-10.698818</v>
@@ -8131,10 +7987,8 @@
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="5" t="n">
+        <v>-1.503519</v>
       </c>
       <c r="F115" s="5" t="n">
         <v>-2.747637</v>
@@ -8170,10 +8024,8 @@
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="5" t="n">
+        <v>-1.503519</v>
       </c>
       <c r="F116" s="5" t="n">
         <v>-2.747637</v>
@@ -8209,10 +8061,8 @@
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="5" t="n">
+        <v>32.21666</v>
       </c>
       <c r="F117" s="5" t="n">
         <v>4.568975</v>
@@ -8250,10 +8100,8 @@
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="5" t="n">
+        <v>-1.392583</v>
       </c>
       <c r="F118" s="5" t="n">
         <v>-0.177438</v>
@@ -8566,10 +8414,8 @@
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="5" t="n">
+        <v>2.3e-06</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>2.7e-06</v>
@@ -10474,10 +10320,8 @@
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E172" s="5" t="n">
+        <v>0.954449</v>
       </c>
       <c r="F172" s="5" t="n">
         <v>0.839713</v>
@@ -10515,10 +10359,8 @@
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E173" s="5" t="n">
+        <v>2.151196</v>
       </c>
       <c r="F173" s="5" t="n">
         <v>2.16757</v>
@@ -10597,10 +10439,8 @@
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E175" s="5" t="n">
+        <v>2.583022</v>
       </c>
       <c r="F175" s="5" t="n">
         <v>1.970427</v>
@@ -10638,10 +10478,8 @@
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E176" s="5" t="n">
+        <v>2.0442</v>
       </c>
       <c r="F176" s="5" t="n">
         <v>1.530555</v>
@@ -10829,94 +10667,100 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Securities lending income (note 9) $</t>
+          <t>For the period ended December 31</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>0.002695</v>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>0.001495</v>
-      </c>
-      <c r="H181" s="5" t="n">
-        <v>0.000713</v>
-      </c>
-      <c r="I181" s="5" t="n">
-        <v>0.00467</v>
+      <c r="E181" s="5" t="n">
+        <v>0.020211</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>from operations</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Net gain (loss) on foreign exchange on cash</t>
+          <t>Net realized (gain) loss on sale of investments (note 8)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>-0.00043</v>
-      </c>
-      <c r="G182" s="5" t="n">
-        <v>-0.028645</v>
-      </c>
-      <c r="H182" s="5" t="n">
-        <v>0.054529</v>
-      </c>
-      <c r="I182" s="5" t="n">
-        <v>0.009124999999999999</v>
+      <c r="E182" s="5" t="n">
+        <v>1.285232</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>from operations</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Interest income for distribution purposes</t>
+          <t>Net realized (gain) loss on options (note 8)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E183" s="5" t="n">
+        <v>0.054923</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -10928,73 +10772,77 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>0.006685</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>0.003203</v>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>from operations</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Dividend income</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>DividendIncome</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>1.733833</v>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>1.6939</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>1.402209</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>1.086895</v>
+          <t>Purchase of investments and options (note 8)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" s="5" t="n">
+        <v>-84.65490699999999</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>from operations</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Distribution income from investment funds</t>
+          <t>Proceeds from sale of investments and options (note 8)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E185" s="5" t="n">
+        <v>25.378287</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -11006,206 +10854,246 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="5" t="n">
-        <v>0.035427</v>
-      </c>
-      <c r="I185" s="5" t="n">
-        <v>0.013341</v>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on sale of investments</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>NetRealizedGainLossOnInvestments</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F186" s="5" t="n">
-        <v>-3.448899</v>
-      </c>
-      <c r="G186" s="5" t="n">
-        <v>-0.320236</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>4.127153</v>
-      </c>
-      <c r="I186" s="5" t="n">
-        <v>8.256594</v>
+          <t>Proceeds from issuance of redeemable Preferred shares (note 4)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" s="5" t="n">
+        <v>32.21666</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Net change in unrealized gain (loss) on investments</t>
+          <t>Proceeds from issuance of redeemable Class J shares (note 4)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>-4.361588</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>3.982445</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>14.017208</v>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>-0.466112</v>
+      <c r="E187" s="5" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on options</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F188" s="5" t="n">
-        <v>0.196293</v>
-      </c>
-      <c r="G188" s="5" t="n">
-        <v>0.08901000000000001</v>
-      </c>
-      <c r="H188" s="5" t="n">
-        <v>-0.396235</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>-0.157907</v>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Net change in unrealized gain (loss) on options</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="n">
-        <v>0.046183</v>
-      </c>
-      <c r="G189" s="5" t="n">
-        <v>-0.033278</v>
-      </c>
-      <c r="H189" s="5" t="n">
-        <v>0.026783</v>
-      </c>
-      <c r="I189" s="5" t="n">
-        <v>-0.016471</v>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>0.370054</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>2   Included in cash flows from operating activities.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on foreign currency forward contracts</t>
+          <t>For the period ended December 31</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F190" s="5" t="n">
-        <v>-2.488609</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>0.041485</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>-1.925767</v>
-      </c>
-      <c r="I190" s="5" t="n">
-        <v>-0.316434</v>
+      <c r="E190" s="5" t="n">
+        <v>0.020211</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>2   Included in cash flows from operating activities.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Net change in unrealized gain (loss) on foreign currency forward contracts</t>
+          <t>Net Assets attributable to holders of redeemable Class A shares at beginning of period $</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -11214,305 +11102,353 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F191" s="5" t="n">
-        <v>0.380379</v>
-      </c>
-      <c r="G191" s="5" t="n">
-        <v>0.707361</v>
-      </c>
-      <c r="H191" s="5" t="n">
-        <v>-1.565129</v>
-      </c>
-      <c r="I191" s="5" t="n">
-        <v>0.980928</v>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Class A shares</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Total net gain (loss) on investments and derivatives</t>
+          <t>Net Assets attributable to holders of redeemable Class A shares at end of period $</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>-7.942408</v>
-      </c>
-      <c r="G192" s="5" t="n">
-        <v>6.163824</v>
-      </c>
-      <c r="H192" s="5" t="n">
-        <v>15.728334</v>
-      </c>
-      <c r="I192" s="5" t="n">
-        <v>9.384036999999999</v>
+      <c r="E192" s="5" t="n">
+        <v>32.503805</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Total income (loss), net</t>
+          <t>Total Asia 2,952,366 3,105,645</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>-7.940143</v>
-      </c>
-      <c r="G193" s="5" t="n">
-        <v>6.136674</v>
-      </c>
-      <c r="H193" s="5" t="n">
-        <v>15.783576</v>
-      </c>
-      <c r="I193" s="5" t="n">
-        <v>9.397831999999999</v>
+      <c r="E193" s="5" t="n">
+        <v>4.8e-06</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Management fees (note 7)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>0.481212</v>
-      </c>
-      <c r="G194" s="5" t="n">
-        <v>0.482259</v>
-      </c>
-      <c r="H194" s="5" t="n">
-        <v>0.508192</v>
-      </c>
-      <c r="I194" s="5" t="n">
-        <v>0.514385</v>
+          <t>Daimler AG 15,500 1,957,474</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>1.508761</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Audit fees</t>
+          <t>Daimler Truck Holding AG 7,750 312,465</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>0.036623</v>
-      </c>
-      <c r="G195" s="5" t="n">
-        <v>0.032081</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>0.032119</v>
-      </c>
-      <c r="I195" s="5" t="n">
-        <v>0.02518</v>
+      <c r="E195" s="5" t="n">
+        <v>0.362625</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Independent Review Committee fees (note 7)</t>
+          <t>Siemens AG 7,300 1,639,107</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>0.003718</v>
-      </c>
-      <c r="G196" s="5" t="n">
-        <v>0.003076</v>
-      </c>
-      <c r="H196" s="5" t="n">
-        <v>0.002257</v>
-      </c>
-      <c r="I196" s="5" t="n">
-        <v>0.002361</v>
+      <c r="E196" s="5" t="n">
+        <v>1.605134</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Custodial fees</t>
+          <t>National Grid PLC 24,000 1,970,681</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="n">
-        <v>0.010865</v>
-      </c>
-      <c r="G197" s="5" t="n">
-        <v>0.013318</v>
-      </c>
-      <c r="H197" s="5" t="n">
-        <v>0.012132</v>
-      </c>
-      <c r="I197" s="5" t="n">
-        <v>0.010155</v>
+      <c r="E197" s="5" t="n">
+        <v>2.195548</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F198" s="5" t="n">
-        <v>0.002971</v>
-      </c>
-      <c r="G198" s="5" t="n">
-        <v>0.003025</v>
-      </c>
-      <c r="H198" s="5" t="n">
-        <v>0.020516</v>
-      </c>
-      <c r="I198" s="5" t="n">
-        <v>0.005351</v>
+          <t>Johnson Controls International PLC 25,600 2,084,828</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="5" t="n">
+        <v>2.633039</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Shareholder reporting costs</t>
+          <t>Linde PLC 5,500 2,001,630</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F199" s="5" t="n">
-        <v>0.025806</v>
-      </c>
-      <c r="G199" s="5" t="n">
-        <v>0.02863</v>
-      </c>
-      <c r="H199" s="5" t="n">
-        <v>0.031441</v>
-      </c>
-      <c r="I199" s="5" t="n">
-        <v>0.031353</v>
+      <c r="E199" s="5" t="n">
+        <v>2.410191</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -11523,35 +11459,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Other administrative expenses</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Securities lending income (note 9) $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F200" s="5" t="n">
-        <v>0.12998</v>
+        <v>0.002695</v>
       </c>
       <c r="G200" s="5" t="n">
-        <v>0.124999</v>
+        <v>0.001495</v>
       </c>
       <c r="H200" s="5" t="n">
-        <v>0.140972</v>
+        <v>0.000713</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>0.125724</v>
+        <v>0.00467</v>
       </c>
     </row>
     <row r="201">
@@ -11562,37 +11494,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net gain (loss) on foreign exchange on cash</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>-0.036928</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>0.000133</v>
+        <v>-0.00043</v>
       </c>
       <c r="G201" s="5" t="n">
-        <v>0.000233</v>
+        <v>-0.028645</v>
       </c>
       <c r="H201" s="5" t="n">
-        <v>0.000114</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.054529</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.009124999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -11603,12 +11527,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
+          <t>Interest income for distribution purposes</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -11617,17 +11541,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F202" s="5" t="n">
-        <v>0.047825</v>
-      </c>
-      <c r="G202" s="5" t="n">
-        <v>0.086895</v>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>0.063302</v>
+        <v>0.006685</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>0.056463</v>
+        <v>0.003203</v>
       </c>
     </row>
     <row r="203">
@@ -11638,35 +11566,33 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Total expenses before withholding taxes</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Dividend income</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DividendIncome</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>1.489762</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>1.733833</v>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>1.6939</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>0.811045</v>
+        <v>1.402209</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>0.770972</v>
+        <v>1.086895</v>
       </c>
     </row>
     <row r="204">
@@ -11677,12 +11603,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Withholding taxes</t>
+          <t>Distribution income from investment funds</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -11691,17 +11617,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F204" s="5" t="n">
-        <v>0.11651</v>
-      </c>
-      <c r="G204" s="5" t="n">
-        <v>0.151647</v>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>0.165257</v>
+        <v>0.035427</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>0.126633</v>
+        <v>0.013341</v>
       </c>
     </row>
     <row r="205">
@@ -11712,33 +11642,35 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Net realized gain (loss) on sale of investments</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetRealizedGainLossOnInvestments</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F205" s="5" t="n">
+        <v>-3.448899</v>
       </c>
       <c r="G205" s="5" t="n">
-        <v>5.210511</v>
+        <v>-0.320236</v>
       </c>
       <c r="H205" s="5" t="n">
-        <v>14.807274</v>
+        <v>4.127153</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>8.500227000000001</v>
+        <v>8.256594</v>
       </c>
     </row>
     <row r="206">
@@ -11749,31 +11681,29 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Distributions on Preferred shares (note 6)</t>
+          <t>Net change in unrealized gain (loss) on investments</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E206" s="5" t="n">
+        <v>7.241422</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>-1.705858</v>
+        <v>-4.361588</v>
       </c>
       <c r="G206" s="5" t="n">
-        <v>-1.842858</v>
+        <v>3.982445</v>
       </c>
       <c r="H206" s="5" t="n">
-        <v>-1.673258</v>
+        <v>14.017208</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>-1.628858</v>
+        <v>-0.466112</v>
       </c>
     </row>
     <row r="207">
@@ -11784,12 +11714,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A $</t>
+          <t>Net realized gain (loss) on options</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -11798,19 +11728,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F207" s="5" t="n">
+        <v>0.196293</v>
       </c>
       <c r="G207" s="5" t="n">
-        <v>3.338285</v>
+        <v>0.08901000000000001</v>
       </c>
       <c r="H207" s="5" t="n">
-        <v>13.134016</v>
+        <v>-0.396235</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>6.871369</v>
+        <v>-0.157907</v>
       </c>
     </row>
     <row r="208">
@@ -11821,33 +11749,29 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A $</t>
+          <t>Net change in unrealized gain (loss) on options</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E208" s="5" t="n">
+        <v>-0.0008319999999999999</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.046183</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>9.000000000000001e-07</v>
+        <v>-0.033278</v>
       </c>
       <c r="H208" s="5" t="n">
-        <v>3.87e-06</v>
+        <v>0.026783</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>2.11e-06</v>
+        <v>-0.016471</v>
       </c>
     </row>
     <row r="209">
@@ -11863,7 +11787,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Interest for distribution purposes</t>
+          <t>Net realized gain (loss) on foreign currency forward contracts</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -11872,21 +11796,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F209" s="5" t="n">
+        <v>-2.488609</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>0.003137</v>
+        <v>0.041485</v>
       </c>
       <c r="H209" s="5" t="n">
-        <v>0.006685</v>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.925767</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>-0.316434</v>
       </c>
     </row>
     <row r="210">
@@ -11897,12 +11817,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Total expenses before taxes</t>
+          <t>Net change in unrealized gain (loss) on foreign currency forward contracts</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -11912,18 +11832,16 @@
         </is>
       </c>
       <c r="F210" s="5" t="n">
-        <v>0.893611</v>
+        <v>0.380379</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>0.774516</v>
+        <v>0.707361</v>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.811045</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.565129</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.980928</v>
       </c>
     </row>
     <row r="211">
@@ -11934,39 +11852,29 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Preferred share premium amortization (note 4)</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>5.749501</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>-0.003232</v>
+        <v>-7.942408</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>-0.029368</v>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.163824</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>15.728334</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>9.384036999999999</v>
       </c>
     </row>
     <row r="212">
@@ -11982,36 +11890,24 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total income (loss), net</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>5.712642</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>-7.940143</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>0.003137</v>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.136674</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>15.783576</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>9.397831999999999</v>
       </c>
     </row>
     <row r="213">
@@ -12027,32 +11923,28 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Agents’ fees and issuance cost on Preferred shares, amortized (note 4)</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management fees (note 7)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="n">
+        <v>0.312678</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>0.154478</v>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.481212</v>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>0.482259</v>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>0.508192</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>0.514385</v>
       </c>
     </row>
     <row r="214">
@@ -12068,36 +11960,24 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Income tax</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Audit fees</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>0.02863</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>0.039464</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.036623</v>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>0.032081</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>0.032119</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>0.02518</v>
       </c>
     </row>
     <row r="215">
@@ -12113,30 +11993,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Net investment income (loss) before distributions on Preferred shares</t>
+          <t>Independent Review Committee fees (note 7)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E215" s="5" t="n">
+        <v>0.005281</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>-8.989727999999999</v>
+        <v>0.003718</v>
       </c>
       <c r="G215" s="5" t="n">
-        <v>5.210511</v>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003076</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>0.002257</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>0.002361</v>
       </c>
     </row>
     <row r="216">
@@ -12152,30 +12026,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A shares $</t>
+          <t>Custodial fees</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E216" s="5" t="n">
+        <v>0.011074</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>-10.698818</v>
+        <v>0.010865</v>
       </c>
       <c r="G216" s="5" t="n">
-        <v>3.338285</v>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013318</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>0.012132</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>0.010155</v>
       </c>
     </row>
     <row r="217">
@@ -12184,35 +12052,35 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>For the period/year ended December 31 2022</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>0.000567</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>0.020211</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002971</v>
+      </c>
+      <c r="G217" s="5" t="n">
+        <v>0.003025</v>
+      </c>
+      <c r="H217" s="5" t="n">
+        <v>0.020516</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>0.005351</v>
       </c>
     </row>
     <row r="218">
@@ -12223,37 +12091,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Securities lending income (note 11) $ 2,695 $</t>
+          <t>Shareholder reporting costs</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E218" s="5" t="n">
+        <v>0.012835</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>6.9e-05</v>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025806</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>0.02863</v>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>0.031441</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>0.031353</v>
       </c>
     </row>
     <row r="219">
@@ -12264,37 +12124,33 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Net gain (loss) on foreign exchange on cash (430)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other administrative expenses</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="n">
+        <v>0.07908800000000001</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>-0.036928</v>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.12998</v>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>0.124999</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>0.140972</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>0.125724</v>
       </c>
     </row>
     <row r="220">
@@ -12305,36 +12161,30 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Dividend income 1,733,833</t>
+          <t>Interest and bank charges</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DividendIncome</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>0.000413</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>1.489762</v>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000133</v>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>0.000233</v>
+      </c>
+      <c r="H220" s="5" t="n">
+        <v>0.000114</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -12350,37 +12200,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on sale of investments (note 8) (3,448,899)</t>
+          <t>Transaction costs</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E221" s="5" t="n">
+        <v>0.108305</v>
       </c>
       <c r="F221" s="5" t="n">
-        <v>-1.285232</v>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.047825</v>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>0.086895</v>
+      </c>
+      <c r="H221" s="5" t="n">
+        <v>0.063302</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>0.056463</v>
       </c>
     </row>
     <row r="222">
@@ -12391,37 +12233,33 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Net change in unrealized gain (loss) on investments (4,361,588)</t>
+          <t>Total expenses before withholding taxes</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" s="5" t="n">
-        <v>7.241422</v>
+      <c r="E222" s="5" t="n">
+        <v>1.468204</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>0.811045</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>0.770972</v>
       </c>
     </row>
     <row r="223">
@@ -12432,37 +12270,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on options (note 8) 196,293</t>
+          <t>Withholding taxes</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E223" s="5" t="n">
+        <v>0.07432999999999999</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>-0.054923</v>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.11651</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>0.151647</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>0.165257</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>0.126633</v>
       </c>
     </row>
     <row r="224">
@@ -12473,12 +12303,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Net change in unrealized gain (loss) on options 46,183</t>
+          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -12487,23 +12317,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F224" s="5" t="n">
-        <v>-0.0008319999999999999</v>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>5.210511</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>14.807274</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>8.500227000000001</v>
       </c>
     </row>
     <row r="225">
@@ -12514,37 +12340,33 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Net realized gain (loss) on foreign currency forward contracts (note 9) (2,488,609)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Distributions on Preferred shares (note 6)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="n">
+        <v>-0.986861</v>
       </c>
       <c r="F225" s="5" t="n">
-        <v>-1.360379</v>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.705858</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>-1.842858</v>
+      </c>
+      <c r="H225" s="5" t="n">
+        <v>-1.673258</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>-1.628858</v>
       </c>
     </row>
     <row r="226">
@@ -12555,12 +12377,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Net change in unrealized gain (loss) on foreign currency forward contracts (note 9) 380,379</t>
+          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -12569,23 +12391,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F226" s="5" t="n">
-        <v>-0.280317</v>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>3.338285</v>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>13.134016</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>6.871369</v>
       </c>
     </row>
     <row r="227">
@@ -12596,12 +12414,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Net gain (loss) on investments and derivatives</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Total net gain (loss) on investments and derivatives (7,942,408)</t>
+          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A $</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -12610,23 +12428,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F227" s="5" t="n">
-        <v>5.749501</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>9.000000000000001e-07</v>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>3.87e-06</v>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>2.11e-06</v>
       </c>
     </row>
     <row r="228">
@@ -12642,7 +12456,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Total income (loss), net (7,940,143)</t>
+          <t>Interest for distribution purposes</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -12651,18 +12465,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F228" s="5" t="n">
-        <v>5.712642</v>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.003137</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>0.006685</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -12683,31 +12495,23 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Management fees (note 7) 481,212</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Total expenses before taxes</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F229" s="5" t="n">
-        <v>0.312678</v>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.893611</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>0.774516</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>0.811045</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -12728,22 +12532,24 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Audit fees 36,623</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Preferred share premium amortization (note 4)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F230" s="5" t="n">
-        <v>0.02863</v>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003232</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>-0.029368</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -12764,27 +12570,31 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Independent Review Committee fees (note 7) 3,718</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F231" s="5" t="n">
-        <v>0.005281</v>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>0.003137</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -12810,17 +12620,15 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Custodial fees 10,865</t>
+          <t>Agents’ fees and issuance cost on Preferred shares, amortized (note 4)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E232" s="5" t="n">
+        <v>0.9093329999999999</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>0.011074</v>
+        <v>0.154478</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -12851,12 +12659,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Legal fees 2,971</t>
+          <t>Income tax</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -12865,7 +12673,7 @@
         </is>
       </c>
       <c r="F233" s="5" t="n">
-        <v>0.000567</v>
+        <v>0.039464</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -12896,22 +12704,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Shareholder reporting costs 25,806</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net investment income (loss) before distributions on Preferred shares</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>4.170108</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>0.012835</v>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.989727999999999</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>5.210511</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -12937,26 +12745,18 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Other administrative expenses 129,980</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A shares $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" s="5" t="n">
+        <v>3.183247</v>
       </c>
       <c r="F235" s="5" t="n">
-        <v>0.07908800000000001</v>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.698818</v>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>3.338285</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -12975,28 +12775,20 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Interest and bank charges 133</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>For the period/year ended December 31 2022</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.000413</v>
+        <v>0.020211</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -13022,12 +12814,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Agents’ fees and issuance cost on Preferred shares, amortized (note 4) 154,478</t>
+          <t>Securities lending income (note 11) $ 2,695 $</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -13037,7 +12829,7 @@
         </is>
       </c>
       <c r="F237" s="5" t="n">
-        <v>0.9093329999999999</v>
+        <v>6.9e-05</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -13063,12 +12855,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Transaction costs 47,825</t>
+          <t>Net gain (loss) on foreign exchange on cash (430)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -13078,7 +12870,7 @@
         </is>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.108305</v>
+        <v>-0.036928</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -13104,22 +12896,26 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Total expenses before taxes 893,611</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Dividend income 1,733,833</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DividendIncome</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F239" s="5" t="n">
-        <v>1.468204</v>
+        <v>1.489762</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -13145,28 +12941,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Income tax 39,464</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Net realized gain (loss) on sale of investments (note 8) (3,448,899)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F240" s="5" t="n">
+        <v>-1.285232</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -13192,12 +12982,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Withholding taxes 116,510</t>
+          <t>Net change in unrealized gain (loss) on investments (4,361,588)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -13207,7 +12997,7 @@
         </is>
       </c>
       <c r="F241" s="5" t="n">
-        <v>0.07432999999999999</v>
+        <v>7.241422</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -13233,12 +13023,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Net investment income (loss) before distributions on Preferred shares (8,989,728)</t>
+          <t>Net realized gain (loss) on options (note 8) 196,293</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -13248,7 +13038,7 @@
         </is>
       </c>
       <c r="F242" s="5" t="n">
-        <v>4.170108</v>
+        <v>-0.054923</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -13274,12 +13064,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Distributions on Preferred shares (note 6) (1,705,858)</t>
+          <t>Net change in unrealized gain (loss) on options 46,183</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -13289,7 +13079,7 @@
         </is>
       </c>
       <c r="F243" s="5" t="n">
-        <v>-0.986861</v>
+        <v>-0.0008319999999999999</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -13315,12 +13105,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Preferred share premium amortization (note 4) (3,232)</t>
+          <t>Net realized gain (loss) on foreign currency forward contracts (note 9) (2,488,609)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -13329,10 +13119,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F244" s="5" t="n">
+        <v>-1.360379</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -13358,12 +13146,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A shares $ (10,698,818) $</t>
+          <t>Net change in unrealized gain (loss) on foreign currency forward contracts (note 9) 380,379</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -13373,7 +13161,7 @@
         </is>
       </c>
       <c r="F245" s="5" t="n">
-        <v>3.183247</v>
+        <v>-0.280317</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -13399,12 +13187,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A shares $ (3.13) $</t>
+          <t>Total net gain (loss) on investments and derivatives (7,942,408)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -13414,7 +13202,7 @@
         </is>
       </c>
       <c r="F246" s="5" t="n">
-        <v>9.900000000000001e-07</v>
+        <v>5.749501</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -13440,12 +13228,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>per share2</t>
+          <t>Net gain (loss) on investments and derivatives</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>1 For the period from May 21, 2021 (commencement of operations) to December 31,</t>
+          <t>Total income (loss), net (7,940,143)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -13455,19 +13243,1068 @@
         </is>
       </c>
       <c r="F247" s="5" t="n">
+        <v>5.712642</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Management fees (note 7) 481,212</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.312678</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Audit fees 36,623</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>0.02863</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Independent Review Committee fees (note 7) 3,718</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>0.005281</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Custodial fees 10,865</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>0.011074</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Legal fees 2,971</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>0.000567</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Shareholder reporting costs 25,806</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>0.012835</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Other administrative expenses 129,980</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>0.07908800000000001</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Interest and bank charges 133</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Agents’ fees and issuance cost on Preferred shares, amortized (note 4) 154,478</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>0.9093329999999999</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Transaction costs 47,825</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>0.108305</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Total expenses before taxes 893,611</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>1.468204</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Income tax 39,464</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Withholding taxes 116,510</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>0.07432999999999999</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Net investment income (loss) before distributions on Preferred shares (8,989,728)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>4.170108</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Distributions on Preferred shares (note 6) (1,705,858)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>-0.986861</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Preferred share premium amortization (note 4) (3,232)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A shares $ (10,698,818) $</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="n">
+        <v>3.183247</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Increase (decrease) in Net Assets attributable to holders of redeemable Class A shares $ (3.13) $</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>9.900000000000001e-07</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>per share2</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>1 For the period from May 21, 2021 (commencement of operations) to December 31,</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="n">
         <v>0.002021</v>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>For the period ended December 31</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" s="5" t="n">
+        <v>0.020211</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Securities lending income (note 11) $</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" s="5" t="n">
+        <v>6.9e-05</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Net realized gain (loss) on sale of investments (note 8)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetRealizedGainLossOnInvestments</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="n">
+        <v>-1.285232</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Net realized gain (loss) on options (note 8)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" s="5" t="n">
+        <v>-0.054923</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Net realized gain (loss) on foreign currency forward contracts (note 9)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" s="5" t="n">
+        <v>-1.360379</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Net gain (loss) on investments and derivatives</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Net change in unrealized gain (loss) on foreign currency forward contracts (note 9)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" s="5" t="n">
+        <v>-0.280317</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
